--- a/Documentation/State.xlsx
+++ b/Documentation/State.xlsx
@@ -503,7 +503,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ورودی‌ها و خروجی‌های دستگاه — بازسازی از کد فعلی (۲۰۲۶-۱۰-۲۴)</t>
+          <t>ورودی‌ها و خروجی‌های دستگاه — بازسازی از کد فعلی (۲۰۲۶-۱۰-۳۱)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>برق ورودی مستقیم (DC). پنجرهٔ سالم ۲۱۰۰۰..۲۸۰۰۰ میلی‌ولت است؛ بیرون از آن خطای ولتاژ/جریان ثبت می‌شود.</t>
+          <t>برق ورودی مستقیم (DC). پنجرهٔ خام q33/q34 (پیش‌فرض ۲۱۰۰۰..۲۸۰۰۰ میلی‌ولت) و حاشیه‌های برگشت q169/q170؛ بیرون پنجره مجوز مشترک ورودی می‌افتد.</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>خروجی سوییچ‌شده بین برق ورودی و باتری. تنها پایهٔ فرمان مسیر، PB11 است (پایه‌های PB5/PB7 هرگز تغییر نمی‌کنند).</t>
+          <t>خروجی سوییچ‌شده بین برق ورودی و باتری. تنها پایهٔ فرمان مسیر، PB11 است؛ PB5 مال McuPowerPath و PB7 مال رلهٔ شارژر است و Changeover به آن‌ها دست نمی‌زند.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>ورودی وصل و شارژ کامل</t>
+          <t>ورودی وصل و اعلام اتمام شارژر یا قفل ولتاژی فول</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>بیشتر از ۲۸۰۰۰ میلی‌ولت (پاک: ≤ ۲۷۰۰۰)</t>
+          <t>بیشتر از سقف مشترک q34 (پاک: ≤ q34−q71؛ پیش‌فرض ۲۸۰۰۰ و ۲۷۰۰۰)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>پمپ &gt; ۱۴٫۸V حین شارژ یا هر نیم &lt; ۶V با ورودی سالم</t>
+          <t>پمپ همان نیم بالای حد قطع حین شارژ، یا یکی از دو نیم زیر آستانهٔ نبود (پیش‌فرض ۶V) با ورودی سالم</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>چشمک‌تند</t>
+          <t>چشمک ۱s با سهم ۵۰٪</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
